--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571451.3091253648</v>
+        <v>571451</v>
       </c>
       <c r="R2" t="n">
-        <v>6427778.131056842</v>
+        <v>6427778</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14103-2025 artfynd.xlsx
+++ b/artfynd/A 14103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74765548</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
